--- a/data/trans_bre/P59A-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P59A-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 6,04</t>
+          <t>-12,59; 5,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 12,34</t>
+          <t>-11,47; 11,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 15,08</t>
+          <t>-6,55; 15,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 10,06</t>
+          <t>-10,06; 11,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,38; 63,06</t>
+          <t>-66,57; 62,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,95; 70,44</t>
+          <t>-40,36; 69,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 93,14</t>
+          <t>-24,11; 86,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,13; 79,29</t>
+          <t>-44,11; 85,4</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 4,82</t>
+          <t>-8,52; 5,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 6,02</t>
+          <t>-8,95; 5,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 3,03</t>
+          <t>-8,54; 3,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 9,29</t>
+          <t>-7,43; 9,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,79; 66,81</t>
+          <t>-55,75; 76,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,44; 52,03</t>
+          <t>-47,08; 49,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,39; 40,15</t>
+          <t>-60,29; 45,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 66,68</t>
+          <t>-29,87; 70,04</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,85; 2,27</t>
+          <t>-15,34; 1,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 5,92</t>
+          <t>-9,49; 7,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 1,99</t>
+          <t>-13,04; 1,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 7,84</t>
+          <t>-5,03; 8,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-72,98; 28,14</t>
+          <t>-70,88; 19,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-63,03; 87,04</t>
+          <t>-66,0; 104,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,39; 24,94</t>
+          <t>-70,05; 23,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,91; 91,85</t>
+          <t>-33,06; 106,07</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 5,95</t>
+          <t>-9,6; 5,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 6,23</t>
+          <t>-13,26; 5,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 2,13</t>
+          <t>-20,25; 0,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,57; -2,25</t>
+          <t>-27,7; -3,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,84; 54,35</t>
+          <t>-49,98; 52,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,99; 37,62</t>
+          <t>-49,81; 34,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,29; 8,84</t>
+          <t>-48,76; 2,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,53; -16,07</t>
+          <t>-79,53; -18,13</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 9,05</t>
+          <t>-13,53; 9,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 16,01</t>
+          <t>-7,25; 15,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,11; 6,27</t>
+          <t>-12,52; 6,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 8,38</t>
+          <t>-6,69; 8,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-56,12; 89,81</t>
+          <t>-62,54; 79,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,14; 269,4</t>
+          <t>-42,69; 271,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-77,12; 141,89</t>
+          <t>-77,18; 135,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 168,26</t>
+          <t>-47,34; 180,3</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 5,62</t>
+          <t>-13,83; 4,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 1,66</t>
+          <t>-16,23; 1,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 4,49</t>
+          <t>-7,43; 5,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 8,96</t>
+          <t>-5,68; 8,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,67; 55,9</t>
+          <t>-62,88; 42,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-86,53; 46,72</t>
+          <t>-85,28; 44,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-75,73; 127,58</t>
+          <t>-71,29; 162,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,16; 104,18</t>
+          <t>-38,97; 106,74</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 0,77</t>
+          <t>-11,04; 0,74</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 8,79</t>
+          <t>-5,79; 7,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 0,18</t>
+          <t>-10,63; -0,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 5,48</t>
+          <t>-7,42; 5,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-61,95; 13,58</t>
+          <t>-61,91; 8,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 64,62</t>
+          <t>-29,19; 59,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-51,68; 3,16</t>
+          <t>-51,03; -0,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-34,1; 45,31</t>
+          <t>-34,39; 45,13</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,56</t>
+          <t>-7,91; 1,92</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 4,76</t>
+          <t>-6,7; 4,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 3,25</t>
+          <t>-7,33; 3,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,27; -3,84</t>
+          <t>-13,12; -4,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,58; 19,79</t>
+          <t>-59,1; 26,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,26; 52,69</t>
+          <t>-43,49; 46,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 24,75</t>
+          <t>-38,76; 26,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-82,39; -40,19</t>
+          <t>-82,68; -39,73</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,06; -0,97</t>
+          <t>-6,08; -0,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,92</t>
+          <t>-3,79; 1,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -0,77</t>
+          <t>-6,25; -0,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -0,06</t>
+          <t>-5,78; 0,05</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-39,67; -7,94</t>
+          <t>-40,28; -6,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-21,95; 14,41</t>
+          <t>-22,49; 13,25</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-31,18; -4,5</t>
+          <t>-33,24; -5,1</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-33,4; -0,59</t>
+          <t>-32,82; 0,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P59A-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P59A-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>-0,42</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>-2,33%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 5,12</t>
+          <t>-13,32; 4,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 11,5</t>
+          <t>-9,9; 12,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 15,28</t>
+          <t>-8,11; 14,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 11,77</t>
+          <t>-9,17; 8,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,57; 62,72</t>
+          <t>-67,31; 49,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,36; 69,64</t>
+          <t>-37,98; 73,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,11; 86,16</t>
+          <t>-28,58; 88,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 85,4</t>
+          <t>-39,49; 65,29</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,78</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 5,79</t>
+          <t>-8,35; 5,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 5,7</t>
+          <t>-9,72; 5,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 3,24</t>
+          <t>-8,83; 3,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 9,4</t>
+          <t>-7,68; 8,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,75; 76,66</t>
+          <t>-53,97; 69,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,08; 49,65</t>
+          <t>-47,73; 49,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,29; 45,33</t>
+          <t>-60,2; 43,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,87; 70,04</t>
+          <t>-30,44; 63,18</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 1,24</t>
+          <t>-15,38; 1,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 7,35</t>
+          <t>-8,55; 6,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,04; 1,76</t>
+          <t>-14,06; 2,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 8,48</t>
+          <t>-7,25; 6,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-70,88; 19,82</t>
+          <t>-71,45; 18,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-66,0; 104,99</t>
+          <t>-62,02; 95,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,05; 23,39</t>
+          <t>-70,35; 28,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-33,06; 106,07</t>
+          <t>-43,05; 73,21</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-13,17</t>
+          <t>-7,62</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-50,56%</t>
+          <t>-30,36%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 5,87</t>
+          <t>-10,22; 6,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 5,56</t>
+          <t>-13,59; 6,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 0,92</t>
+          <t>-19,93; 1,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-27,7; -3,58</t>
+          <t>-18,6; 1,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,98; 52,58</t>
+          <t>-50,2; 68,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,81; 34,6</t>
+          <t>-51,13; 39,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,76; 2,96</t>
+          <t>-47,14; 4,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,53; -18,13</t>
+          <t>-54,87; 19,1</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 9,09</t>
+          <t>-12,6; 9,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 15,26</t>
+          <t>-6,71; 15,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 6,49</t>
+          <t>-11,96; 5,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 8,56</t>
+          <t>-5,01; 9,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-62,54; 79,48</t>
+          <t>-60,37; 88,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 271,99</t>
+          <t>-42,53; 249,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-77,18; 135,85</t>
+          <t>-78,94; 124,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-47,34; 180,3</t>
+          <t>-44,1; 222,6</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 4,93</t>
+          <t>-13,61; 4,94</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 1,69</t>
+          <t>-15,45; 2,12</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 5,18</t>
+          <t>-8,69; 4,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 8,72</t>
+          <t>-6,36; 8,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,88; 42,47</t>
+          <t>-59,86; 42,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-85,28; 44,18</t>
+          <t>-87,31; 47,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,29; 162,57</t>
+          <t>-78,75; 122,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,97; 106,74</t>
+          <t>-41,34; 103,94</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,38</t>
+          <t>0,16</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-2,34%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 0,74</t>
+          <t>-11,88; 0,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 7,84</t>
+          <t>-5,38; 7,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,63; -0,01</t>
+          <t>-11,15; -0,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 5,79</t>
+          <t>-6,74; 5,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-61,91; 8,73</t>
+          <t>-66,49; 3,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-29,19; 59,49</t>
+          <t>-27,38; 61,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-51,03; -0,52</t>
+          <t>-53,11; -0,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 45,13</t>
+          <t>-31,77; 44,17</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-8,33</t>
+          <t>-8,4</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-67,02%</t>
+          <t>-65,74%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 1,92</t>
+          <t>-7,94; 2,07</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 4,35</t>
+          <t>-6,02; 4,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 3,33</t>
+          <t>-7,11; 3,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,12; -4,0</t>
+          <t>-13,13; -3,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,1; 26,8</t>
+          <t>-60,27; 27,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,49; 46,51</t>
+          <t>-42,0; 48,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,76; 26,56</t>
+          <t>-38,41; 22,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-82,68; -39,73</t>
+          <t>-81,29; -33,46</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-2,79</t>
+          <t>-2,54</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-17,61%</t>
+          <t>-15,55%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,08; -0,73</t>
+          <t>-6,01; -0,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,88</t>
+          <t>-3,86; 2,12</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,25; -0,79</t>
+          <t>-6,09; -0,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,05</t>
+          <t>-5,1; 0,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-40,28; -6,54</t>
+          <t>-39,84; -6,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 13,25</t>
+          <t>-23,19; 15,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-33,24; -5,1</t>
+          <t>-32,59; -4,23</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-32,82; 0,95</t>
+          <t>-28,53; 2,49</t>
         </is>
       </c>
     </row>
